--- a/artfynd/A 18719-2024 artfynd.xlsx
+++ b/artfynd/A 18719-2024 artfynd.xlsx
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117753420</v>
+        <v>117753453</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421699</v>
+        <v>421822</v>
       </c>
       <c r="R22" t="n">
-        <v>7053427</v>
+        <v>7053459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117753453</v>
+        <v>117753454</v>
       </c>
       <c r="B23" t="n">
         <v>90517</v>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421822</v>
+        <v>421714</v>
       </c>
       <c r="R23" t="n">
-        <v>7053459</v>
+        <v>7053535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117753454</v>
+        <v>117753420</v>
       </c>
       <c r="B24" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421714</v>
+        <v>421699</v>
       </c>
       <c r="R24" t="n">
-        <v>7053535</v>
+        <v>7053427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,6 +3095,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18719-2024 artfynd.xlsx
+++ b/artfynd/A 18719-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753429</v>
+        <v>117753379</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421760</v>
+        <v>421648</v>
       </c>
       <c r="R2" t="n">
-        <v>7053485</v>
+        <v>7053492</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753382</v>
+        <v>117753433</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421661</v>
+        <v>421770</v>
       </c>
       <c r="R3" t="n">
-        <v>7053466</v>
+        <v>7053482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753424</v>
+        <v>117753445</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421729</v>
+        <v>421687</v>
       </c>
       <c r="R4" t="n">
-        <v>7053440</v>
+        <v>7053665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753384</v>
+        <v>117753420</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421681</v>
+        <v>421699</v>
       </c>
       <c r="R5" t="n">
-        <v>7053367</v>
+        <v>7053427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753434</v>
+        <v>117753426</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421773</v>
+        <v>421749</v>
       </c>
       <c r="R6" t="n">
-        <v>7053491</v>
+        <v>7053494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753375</v>
+        <v>117753365</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421637</v>
+        <v>421647</v>
       </c>
       <c r="R7" t="n">
-        <v>7053550</v>
+        <v>7053657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753414</v>
+        <v>117753428</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421827</v>
+        <v>421766</v>
       </c>
       <c r="R9" t="n">
-        <v>7053334</v>
+        <v>7053502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre på 2 granar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753443</v>
+        <v>117753384</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421684</v>
+        <v>421681</v>
       </c>
       <c r="R10" t="n">
-        <v>7053610</v>
+        <v>7053367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753426</v>
+        <v>117753429</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421749</v>
+        <v>421760</v>
       </c>
       <c r="R11" t="n">
-        <v>7053494</v>
+        <v>7053485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753442</v>
+        <v>117753377</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421688</v>
+        <v>421639</v>
       </c>
       <c r="R12" t="n">
-        <v>7053546</v>
+        <v>7053552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117753366</v>
+        <v>117753438</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421626</v>
+        <v>421714</v>
       </c>
       <c r="R13" t="n">
-        <v>7053636</v>
+        <v>7053535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753431</v>
+        <v>117753373</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421761</v>
+        <v>421620</v>
       </c>
       <c r="R14" t="n">
-        <v>7053480</v>
+        <v>7053557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117753381</v>
+        <v>117753435</v>
       </c>
       <c r="B15" t="n">
         <v>57287</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421655</v>
+        <v>421779</v>
       </c>
       <c r="R15" t="n">
-        <v>7053494</v>
+        <v>7053492</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117753372</v>
+        <v>117753441</v>
       </c>
       <c r="B16" t="n">
         <v>57287</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421604</v>
+        <v>421742</v>
       </c>
       <c r="R16" t="n">
-        <v>7053542</v>
+        <v>7053578</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753423</v>
+        <v>117753372</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421718</v>
+        <v>421604</v>
       </c>
       <c r="R17" t="n">
-        <v>7053427</v>
+        <v>7053542</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753435</v>
+        <v>117753419</v>
       </c>
       <c r="B18" t="n">
         <v>57287</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421779</v>
+        <v>421721</v>
       </c>
       <c r="R18" t="n">
-        <v>7053492</v>
+        <v>7053411</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117753437</v>
+        <v>117753432</v>
       </c>
       <c r="B19" t="n">
         <v>57287</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421728</v>
+        <v>421763</v>
       </c>
       <c r="R19" t="n">
-        <v>7053527</v>
+        <v>7053488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117753365</v>
+        <v>117753424</v>
       </c>
       <c r="B20" t="n">
         <v>57287</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421647</v>
+        <v>421729</v>
       </c>
       <c r="R20" t="n">
-        <v>7053657</v>
+        <v>7053440</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117753416</v>
+        <v>117753413</v>
       </c>
       <c r="B21" t="n">
         <v>57287</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421713</v>
+        <v>421846</v>
       </c>
       <c r="R21" t="n">
-        <v>7053360</v>
+        <v>7053341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117753453</v>
+        <v>117753443</v>
       </c>
       <c r="B22" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421822</v>
+        <v>421684</v>
       </c>
       <c r="R22" t="n">
-        <v>7053459</v>
+        <v>7053610</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,6 +2891,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117753454</v>
+        <v>117753416</v>
       </c>
       <c r="B23" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421714</v>
+        <v>421713</v>
       </c>
       <c r="R23" t="n">
-        <v>7053535</v>
+        <v>7053360</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,6 +2998,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117753420</v>
+        <v>117753456</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421699</v>
+        <v>421677</v>
       </c>
       <c r="R24" t="n">
-        <v>7053427</v>
+        <v>7053682</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,11 +3105,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117753417</v>
+        <v>117753378</v>
       </c>
       <c r="B25" t="n">
         <v>57287</v>
@@ -3166,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421720</v>
+        <v>421653</v>
       </c>
       <c r="R25" t="n">
-        <v>7053373</v>
+        <v>7053505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117753378</v>
+        <v>117753414</v>
       </c>
       <c r="B26" t="n">
         <v>57287</v>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421653</v>
+        <v>421827</v>
       </c>
       <c r="R26" t="n">
-        <v>7053505</v>
+        <v>7053334</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och äldre på 2 granar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117753413</v>
+        <v>117753415</v>
       </c>
       <c r="B27" t="n">
         <v>57287</v>
@@ -3380,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421846</v>
+        <v>421728</v>
       </c>
       <c r="R27" t="n">
-        <v>7053341</v>
+        <v>7053349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3425,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117753415</v>
+        <v>117753381</v>
       </c>
       <c r="B28" t="n">
         <v>57287</v>
@@ -3487,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421728</v>
+        <v>421655</v>
       </c>
       <c r="R28" t="n">
-        <v>7053349</v>
+        <v>7053494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,7 +3559,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117753432</v>
+        <v>117753375</v>
       </c>
       <c r="B29" t="n">
         <v>57287</v>
@@ -3594,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421763</v>
+        <v>421637</v>
       </c>
       <c r="R29" t="n">
-        <v>7053488</v>
+        <v>7053550</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3639,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,7 +3666,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117753445</v>
+        <v>117753423</v>
       </c>
       <c r="B30" t="n">
         <v>57287</v>
@@ -3701,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421687</v>
+        <v>421718</v>
       </c>
       <c r="R30" t="n">
-        <v>7053665</v>
+        <v>7053427</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3746,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3773,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117753438</v>
+        <v>117753382</v>
       </c>
       <c r="B31" t="n">
         <v>57287</v>
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421714</v>
+        <v>421661</v>
       </c>
       <c r="R31" t="n">
-        <v>7053535</v>
+        <v>7053466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3853,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,7 +3880,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117753425</v>
+        <v>117753434</v>
       </c>
       <c r="B32" t="n">
         <v>57287</v>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421726</v>
+        <v>421773</v>
       </c>
       <c r="R32" t="n">
-        <v>7053439</v>
+        <v>7053491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3960,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,7 +3987,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117753412</v>
+        <v>117753370</v>
       </c>
       <c r="B33" t="n">
         <v>57287</v>
@@ -4022,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421861</v>
+        <v>421573</v>
       </c>
       <c r="R33" t="n">
-        <v>7053314</v>
+        <v>7053618</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4067,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4089,10 +4094,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117753456</v>
+        <v>117753444</v>
       </c>
       <c r="B34" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4105,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4129,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421677</v>
+        <v>421694</v>
       </c>
       <c r="R34" t="n">
-        <v>7053682</v>
+        <v>7053641</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4165,6 +4170,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4201,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117753371</v>
+        <v>117753412</v>
       </c>
       <c r="B35" t="n">
         <v>57287</v>
@@ -4231,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421600</v>
+        <v>421861</v>
       </c>
       <c r="R35" t="n">
-        <v>7053569</v>
+        <v>7053314</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4271,7 +4281,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4298,10 +4308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117753418</v>
+        <v>117753453</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421695</v>
+        <v>421822</v>
       </c>
       <c r="R36" t="n">
-        <v>7053381</v>
+        <v>7053459</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,11 +4384,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117753428</v>
+        <v>117753425</v>
       </c>
       <c r="B37" t="n">
         <v>57287</v>
@@ -4445,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421766</v>
+        <v>421726</v>
       </c>
       <c r="R37" t="n">
-        <v>7053502</v>
+        <v>7053439</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117753444</v>
+        <v>117753421</v>
       </c>
       <c r="B38" t="n">
         <v>57287</v>
@@ -4552,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421694</v>
+        <v>421703</v>
       </c>
       <c r="R38" t="n">
-        <v>7053641</v>
+        <v>7053427</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4597,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,7 +4624,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117753364</v>
+        <v>117753371</v>
       </c>
       <c r="B39" t="n">
         <v>57287</v>
@@ -4659,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>421636</v>
+        <v>421600</v>
       </c>
       <c r="R39" t="n">
-        <v>7053682</v>
+        <v>7053569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4704,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,7 +4731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117753373</v>
+        <v>117753442</v>
       </c>
       <c r="B40" t="n">
         <v>57287</v>
@@ -4766,10 +4771,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>421620</v>
+        <v>421688</v>
       </c>
       <c r="R40" t="n">
-        <v>7053557</v>
+        <v>7053546</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,7 +4838,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117753421</v>
+        <v>117753417</v>
       </c>
       <c r="B41" t="n">
         <v>57287</v>
@@ -4873,10 +4878,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421703</v>
+        <v>421720</v>
       </c>
       <c r="R41" t="n">
-        <v>7053427</v>
+        <v>7053373</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,7 +4918,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4940,7 +4945,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117753370</v>
+        <v>117753431</v>
       </c>
       <c r="B42" t="n">
         <v>57287</v>
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421573</v>
+        <v>421761</v>
       </c>
       <c r="R42" t="n">
-        <v>7053618</v>
+        <v>7053480</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,7 +5025,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5047,7 +5052,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117753379</v>
+        <v>117753437</v>
       </c>
       <c r="B43" t="n">
         <v>57287</v>
@@ -5087,10 +5092,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421648</v>
+        <v>421728</v>
       </c>
       <c r="R43" t="n">
-        <v>7053492</v>
+        <v>7053527</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5154,7 +5159,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117753419</v>
+        <v>117753418</v>
       </c>
       <c r="B44" t="n">
         <v>57287</v>
@@ -5194,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421721</v>
+        <v>421695</v>
       </c>
       <c r="R44" t="n">
-        <v>7053411</v>
+        <v>7053381</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,7 +5239,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,7 +5266,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117753377</v>
+        <v>117753366</v>
       </c>
       <c r="B45" t="n">
         <v>57287</v>
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421639</v>
+        <v>421626</v>
       </c>
       <c r="R45" t="n">
-        <v>7053552</v>
+        <v>7053636</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5368,7 +5373,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117753433</v>
+        <v>117753364</v>
       </c>
       <c r="B46" t="n">
         <v>57287</v>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>421770</v>
+        <v>421636</v>
       </c>
       <c r="R46" t="n">
-        <v>7053482</v>
+        <v>7053682</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5453,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,10 +5480,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117753441</v>
+        <v>117753454</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5491,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>421742</v>
+        <v>421714</v>
       </c>
       <c r="R47" t="n">
-        <v>7053578</v>
+        <v>7053535</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5551,11 +5556,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 18719-2024 artfynd.xlsx
+++ b/artfynd/A 18719-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753379</v>
+        <v>117753416</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421648</v>
+        <v>421713</v>
       </c>
       <c r="R2" t="n">
-        <v>7053492</v>
+        <v>7053360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753433</v>
+        <v>117753366</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421770</v>
+        <v>421626</v>
       </c>
       <c r="R3" t="n">
-        <v>7053482</v>
+        <v>7053636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753445</v>
+        <v>117753375</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421687</v>
+        <v>421637</v>
       </c>
       <c r="R4" t="n">
-        <v>7053665</v>
+        <v>7053550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753420</v>
+        <v>117753364</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421699</v>
+        <v>421636</v>
       </c>
       <c r="R5" t="n">
-        <v>7053427</v>
+        <v>7053682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753426</v>
+        <v>117753428</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421749</v>
+        <v>421766</v>
       </c>
       <c r="R6" t="n">
-        <v>7053494</v>
+        <v>7053502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753365</v>
+        <v>117753377</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421647</v>
+        <v>421639</v>
       </c>
       <c r="R7" t="n">
-        <v>7053657</v>
+        <v>7053552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753427</v>
+        <v>117753445</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421759</v>
+        <v>421687</v>
       </c>
       <c r="R8" t="n">
-        <v>7053506</v>
+        <v>7053665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753428</v>
+        <v>117753431</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421766</v>
+        <v>421761</v>
       </c>
       <c r="R9" t="n">
-        <v>7053502</v>
+        <v>7053480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753384</v>
+        <v>117753456</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421681</v>
+        <v>421677</v>
       </c>
       <c r="R10" t="n">
-        <v>7053367</v>
+        <v>7053682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753429</v>
+        <v>117753443</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421760</v>
+        <v>421684</v>
       </c>
       <c r="R11" t="n">
-        <v>7053485</v>
+        <v>7053610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753377</v>
+        <v>117753415</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421639</v>
+        <v>421728</v>
       </c>
       <c r="R12" t="n">
-        <v>7053552</v>
+        <v>7053349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117753438</v>
+        <v>117753365</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421714</v>
+        <v>421647</v>
       </c>
       <c r="R13" t="n">
-        <v>7053535</v>
+        <v>7053657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753373</v>
+        <v>117753379</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421620</v>
+        <v>421648</v>
       </c>
       <c r="R14" t="n">
-        <v>7053557</v>
+        <v>7053492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117753435</v>
+        <v>117753434</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421779</v>
+        <v>421773</v>
       </c>
       <c r="R15" t="n">
-        <v>7053492</v>
+        <v>7053491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2171,7 @@
         <v>117753441</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753372</v>
+        <v>117753425</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421604</v>
+        <v>421726</v>
       </c>
       <c r="R17" t="n">
-        <v>7053542</v>
+        <v>7053439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753419</v>
+        <v>117753417</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421721</v>
+        <v>421720</v>
       </c>
       <c r="R18" t="n">
-        <v>7053411</v>
+        <v>7053373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117753432</v>
+        <v>117753381</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421763</v>
+        <v>421655</v>
       </c>
       <c r="R19" t="n">
-        <v>7053488</v>
+        <v>7053494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117753424</v>
+        <v>117753444</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421729</v>
+        <v>421694</v>
       </c>
       <c r="R20" t="n">
-        <v>7053440</v>
+        <v>7053641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117753413</v>
+        <v>117753418</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421846</v>
+        <v>421695</v>
       </c>
       <c r="R21" t="n">
-        <v>7053341</v>
+        <v>7053381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117753443</v>
+        <v>117753423</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421684</v>
+        <v>421718</v>
       </c>
       <c r="R22" t="n">
-        <v>7053610</v>
+        <v>7053427</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117753416</v>
+        <v>117753414</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421713</v>
+        <v>421827</v>
       </c>
       <c r="R23" t="n">
-        <v>7053360</v>
+        <v>7053334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre på 2 granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117753456</v>
+        <v>117753433</v>
       </c>
       <c r="B24" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421677</v>
+        <v>421770</v>
       </c>
       <c r="R24" t="n">
-        <v>7053682</v>
+        <v>7053482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,6 +3100,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117753378</v>
+        <v>117753412</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421653</v>
+        <v>421861</v>
       </c>
       <c r="R25" t="n">
-        <v>7053505</v>
+        <v>7053314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117753414</v>
+        <v>117753370</v>
       </c>
       <c r="B26" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421827</v>
+        <v>421573</v>
       </c>
       <c r="R26" t="n">
-        <v>7053334</v>
+        <v>7053618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre på 2 granar</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117753415</v>
+        <v>117753373</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421728</v>
+        <v>421620</v>
       </c>
       <c r="R27" t="n">
-        <v>7053349</v>
+        <v>7053557</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117753381</v>
+        <v>117753421</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421655</v>
+        <v>421703</v>
       </c>
       <c r="R28" t="n">
-        <v>7053494</v>
+        <v>7053427</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117753375</v>
+        <v>117753378</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421637</v>
+        <v>421653</v>
       </c>
       <c r="R29" t="n">
-        <v>7053550</v>
+        <v>7053505</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117753423</v>
+        <v>117753432</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421718</v>
+        <v>421763</v>
       </c>
       <c r="R30" t="n">
-        <v>7053427</v>
+        <v>7053488</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117753382</v>
+        <v>117753413</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421661</v>
+        <v>421846</v>
       </c>
       <c r="R31" t="n">
-        <v>7053466</v>
+        <v>7053341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117753434</v>
+        <v>117753454</v>
       </c>
       <c r="B32" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421773</v>
+        <v>421714</v>
       </c>
       <c r="R32" t="n">
-        <v>7053491</v>
+        <v>7053535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,11 +3956,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,10 +3982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117753370</v>
+        <v>117753372</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4027,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421573</v>
+        <v>421604</v>
       </c>
       <c r="R33" t="n">
-        <v>7053618</v>
+        <v>7053542</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,7 +4062,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,10 +4089,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117753444</v>
+        <v>117753438</v>
       </c>
       <c r="B34" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4134,10 +4129,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421694</v>
+        <v>421714</v>
       </c>
       <c r="R34" t="n">
-        <v>7053641</v>
+        <v>7053535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4201,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117753412</v>
+        <v>117753419</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421861</v>
+        <v>421721</v>
       </c>
       <c r="R35" t="n">
-        <v>7053314</v>
+        <v>7053411</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4276,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4308,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117753453</v>
+        <v>117753429</v>
       </c>
       <c r="B36" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4324,21 +4319,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421822</v>
+        <v>421760</v>
       </c>
       <c r="R36" t="n">
-        <v>7053459</v>
+        <v>7053485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,6 +4379,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,10 +4410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117753425</v>
+        <v>117753420</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421726</v>
+        <v>421699</v>
       </c>
       <c r="R37" t="n">
-        <v>7053439</v>
+        <v>7053427</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117753421</v>
+        <v>117753435</v>
       </c>
       <c r="B38" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421703</v>
+        <v>421779</v>
       </c>
       <c r="R38" t="n">
-        <v>7053427</v>
+        <v>7053492</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117753371</v>
+        <v>117753382</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>421600</v>
+        <v>421661</v>
       </c>
       <c r="R39" t="n">
-        <v>7053569</v>
+        <v>7053466</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117753442</v>
+        <v>117753426</v>
       </c>
       <c r="B40" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>421688</v>
+        <v>421749</v>
       </c>
       <c r="R40" t="n">
-        <v>7053546</v>
+        <v>7053494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117753417</v>
+        <v>117753371</v>
       </c>
       <c r="B41" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421720</v>
+        <v>421600</v>
       </c>
       <c r="R41" t="n">
-        <v>7053373</v>
+        <v>7053569</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117753431</v>
+        <v>117753442</v>
       </c>
       <c r="B42" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421761</v>
+        <v>421688</v>
       </c>
       <c r="R42" t="n">
-        <v>7053480</v>
+        <v>7053546</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5055,7 +5055,7 @@
         <v>117753437</v>
       </c>
       <c r="B43" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117753418</v>
+        <v>117753427</v>
       </c>
       <c r="B44" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421695</v>
+        <v>421759</v>
       </c>
       <c r="R44" t="n">
-        <v>7053381</v>
+        <v>7053506</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5266,10 +5266,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117753366</v>
+        <v>117753424</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421626</v>
+        <v>421729</v>
       </c>
       <c r="R45" t="n">
-        <v>7053636</v>
+        <v>7053440</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117753364</v>
+        <v>117753453</v>
       </c>
       <c r="B46" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5389,21 +5389,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>421636</v>
+        <v>421822</v>
       </c>
       <c r="R46" t="n">
-        <v>7053682</v>
+        <v>7053459</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5449,11 +5449,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5480,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117753454</v>
+        <v>117753384</v>
       </c>
       <c r="B47" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5496,21 +5491,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>421714</v>
+        <v>421681</v>
       </c>
       <c r="R47" t="n">
-        <v>7053535</v>
+        <v>7053367</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,6 +5551,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 18719-2024 artfynd.xlsx
+++ b/artfynd/A 18719-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117753381</v>
+        <v>117753423</v>
       </c>
       <c r="B19" t="n">
         <v>57288</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421655</v>
+        <v>421718</v>
       </c>
       <c r="R19" t="n">
-        <v>7053494</v>
+        <v>7053427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117753444</v>
+        <v>117753381</v>
       </c>
       <c r="B20" t="n">
         <v>57288</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421694</v>
+        <v>421655</v>
       </c>
       <c r="R20" t="n">
-        <v>7053641</v>
+        <v>7053494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117753418</v>
+        <v>117753444</v>
       </c>
       <c r="B21" t="n">
         <v>57288</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421695</v>
+        <v>421694</v>
       </c>
       <c r="R21" t="n">
-        <v>7053381</v>
+        <v>7053641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117753423</v>
+        <v>117753418</v>
       </c>
       <c r="B22" t="n">
         <v>57288</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421718</v>
+        <v>421695</v>
       </c>
       <c r="R22" t="n">
-        <v>7053427</v>
+        <v>7053381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
